--- a/erechnung/E-Rechnung_Arbeitsmappe.xlsx
+++ b/erechnung/E-Rechnung_Arbeitsmappe.xlsx
@@ -128,7 +128,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -148,6 +148,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F2F1EC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -221,7 +226,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -288,6 +293,16 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -688,6 +703,13 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="29" t="inlineStr">
+        <is>
+          <t>Drei Zeilen sind vorrecherchiert (04.09.2026). Weiss = belegt. Gelb = noch offen. Quellen stehen in Spalte O.</t>
+        </is>
+      </c>
+    </row>
     <row r="4" ht="26" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -847,7 +869,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="30" customHeight="1">
+    <row r="7" ht="86" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
           <t>lexoffice / Lexware Office</t>
@@ -863,20 +885,66 @@
           <t>Kern</t>
         </is>
       </c>
-      <c r="D7" s="9" t="n"/>
-      <c r="E7" s="9" t="n"/>
-      <c r="F7" s="9" t="n"/>
-      <c r="G7" s="9" t="n"/>
-      <c r="H7" s="9" t="n"/>
-      <c r="I7" s="9" t="n"/>
-      <c r="J7" s="9" t="n"/>
-      <c r="K7" s="9" t="n"/>
-      <c r="L7" s="9" t="n"/>
-      <c r="M7" s="9" t="n"/>
-      <c r="N7" s="9" t="n"/>
-      <c r="O7" s="9" t="n"/>
-    </row>
-    <row r="8" ht="30" customHeight="1">
+      <c r="D7" s="30" t="inlineStr">
+        <is>
+          <t>04.09.2026</t>
+        </is>
+      </c>
+      <c r="E7" s="30" t="inlineStr">
+        <is>
+          <t>ab Paket M</t>
+        </is>
+      </c>
+      <c r="F7" s="30" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="G7" s="30" t="inlineStr">
+        <is>
+          <t>XRechnung + ZUGFeRD</t>
+        </is>
+      </c>
+      <c r="H7" s="30" t="inlineStr">
+        <is>
+          <t>Einstellungen (Zahnrad) &gt; E-Rechnung &gt; „E-Rechnung erstellen“. Admin-Rechte noetig.</t>
+        </is>
+      </c>
+      <c r="I7" s="30" t="inlineStr">
+        <is>
+          <t>Kontakt muss als „Firma“ angelegt sein — an Privatpersonen ist keine E-Rechnung moeglich. Bei Behoerden zusaetzlich Leitweg-ID und Lieferantennummer.</t>
+        </is>
+      </c>
+      <c r="J7" s="31" t="inlineStr">
+        <is>
+          <t>NEIN — nur als PDF! Rechnungsart oben rechts „§13b – Bauleistung“, vorher im Kundenstamm &gt; Steuerangaben Haekchen „Steuerfreie Rechnungen erlauben“. Lexware selbst: §13b wird aktuell NICHT im XRechnung- oder ZUGFeRD-Format unterstuetzt.</t>
+        </is>
+      </c>
+      <c r="K7" s="30" t="inlineStr">
+        <is>
+          <t>Kundenstamm, Pflichtfeld bei Behoerden</t>
+        </is>
+      </c>
+      <c r="L7" s="30" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="M7" s="31" t="inlineStr">
+        <is>
+          <t>GROESSTER PUNKT: Baubetriebe mit §13b koennen mit Lexware Office ab 2028 keine gueltige E-Rechnung stellen. Bis 2027/2028 ist PDF noch zulaessig, danach nicht mehr. Das ist kein Einrichtungsauftrag, sondern ein Gespraech ueber einen Systemwechsel.</t>
+        </is>
+      </c>
+      <c r="N7" s="30" t="n">
+        <v>2</v>
+      </c>
+      <c r="O7" s="30" t="inlineStr">
+        <is>
+          <t>help.lexware.de/de-form/articles/547939 und /547981</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="86" customHeight="1">
       <c r="A8" s="6" t="inlineStr">
         <is>
           <t>sevdesk</t>
@@ -892,18 +960,62 @@
           <t>Kern</t>
         </is>
       </c>
-      <c r="D8" s="9" t="n"/>
-      <c r="E8" s="9" t="n"/>
-      <c r="F8" s="9" t="n"/>
-      <c r="G8" s="9" t="n"/>
-      <c r="H8" s="9" t="n"/>
-      <c r="I8" s="9" t="n"/>
-      <c r="J8" s="9" t="n"/>
-      <c r="K8" s="9" t="n"/>
-      <c r="L8" s="9" t="n"/>
-      <c r="M8" s="9" t="n"/>
+      <c r="D8" s="30" t="inlineStr">
+        <is>
+          <t>04.09.2026</t>
+        </is>
+      </c>
+      <c r="E8" s="32" t="inlineStr">
+        <is>
+          <t>— noch offen —</t>
+        </is>
+      </c>
+      <c r="F8" s="30" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="G8" s="30" t="inlineStr">
+        <is>
+          <t>XRechnung (UBL) + ZUGFeRD 2.1 / 2.2</t>
+        </is>
+      </c>
+      <c r="H8" s="30" t="inlineStr">
+        <is>
+          <t>Einstellungen &gt; Rechnungen: Standardformat auf XRechnung oder ZUGFeRD setzen. QUELLE DRITTANBIETER — in der sevdesk-Hilfe gegenpruefen.</t>
+        </is>
+      </c>
+      <c r="I8" s="30" t="inlineStr">
+        <is>
+          <t>USt-IdNr., Bankverbindung, Handelsregisternummer unter Einstellungen &gt; Unternehmen</t>
+        </is>
+      </c>
+      <c r="J8" s="32" t="inlineStr">
+        <is>
+          <t>— noch offen — — unbedingt selbst pruefen, siehe Lexware-Zeile</t>
+        </is>
+      </c>
+      <c r="K8" s="30" t="inlineStr">
+        <is>
+          <t>im Kontaktdatensatz des Empfaengers</t>
+        </is>
+      </c>
+      <c r="L8" s="32" t="inlineStr">
+        <is>
+          <t>— noch offen —</t>
+        </is>
+      </c>
+      <c r="M8" s="30" t="inlineStr">
+        <is>
+          <t>Angaben stammen aus Drittquellen, nicht aus der Herstellerhilfe. Vor dem ersten Kunden verifizieren.</t>
+        </is>
+      </c>
       <c r="N8" s="9" t="n"/>
-      <c r="O8" s="9" t="n"/>
+      <c r="O8" s="30" t="inlineStr">
+        <is>
+          <t>sevdesk.de/funktion-e-rechnung (Herstellerhilfe noch pruefen)</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
@@ -934,7 +1046,7 @@
       <c r="N9" s="9" t="n"/>
       <c r="O9" s="9" t="n"/>
     </row>
-    <row r="10" ht="30" customHeight="1">
+    <row r="10" ht="86" customHeight="1">
       <c r="A10" s="6" t="inlineStr">
         <is>
           <t>easybill</t>
@@ -950,18 +1062,62 @@
           <t>Kern</t>
         </is>
       </c>
-      <c r="D10" s="9" t="n"/>
-      <c r="E10" s="9" t="n"/>
-      <c r="F10" s="9" t="n"/>
-      <c r="G10" s="9" t="n"/>
-      <c r="H10" s="9" t="n"/>
-      <c r="I10" s="9" t="n"/>
-      <c r="J10" s="9" t="n"/>
-      <c r="K10" s="9" t="n"/>
-      <c r="L10" s="9" t="n"/>
-      <c r="M10" s="9" t="n"/>
+      <c r="D10" s="30" t="inlineStr">
+        <is>
+          <t>04.09.2026</t>
+        </is>
+      </c>
+      <c r="E10" s="32" t="inlineStr">
+        <is>
+          <t>— noch offen —</t>
+        </is>
+      </c>
+      <c r="F10" s="30" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="G10" s="30" t="inlineStr">
+        <is>
+          <t>XRechnung 3.0.2 + ZUGFeRD</t>
+        </is>
+      </c>
+      <c r="H10" s="30" t="inlineStr">
+        <is>
+          <t>Kunde oeffnen &gt; Bearbeiten &gt; Einstellungen &gt; Dokumentformat fuer den Versand. Wird JE KUNDE eingestellt, nicht zentral.</t>
+        </is>
+      </c>
+      <c r="I10" s="32" t="inlineStr">
+        <is>
+          <t>— noch offen —</t>
+        </is>
+      </c>
+      <c r="J10" s="32" t="inlineStr">
+        <is>
+          <t>— noch offen — — unbedingt selbst pruefen</t>
+        </is>
+      </c>
+      <c r="K10" s="32" t="inlineStr">
+        <is>
+          <t>— noch offen —</t>
+        </is>
+      </c>
+      <c r="L10" s="32" t="inlineStr">
+        <is>
+          <t>— noch offen —</t>
+        </is>
+      </c>
+      <c r="M10" s="30" t="inlineStr">
+        <is>
+          <t>Format je Kunde statt global — bei vielen Bestandskunden entsteht Mehraufwand. Hersteller empfiehlt, ZUGFeRD als Standard fuer alle Vorlagen zu setzen.</t>
+        </is>
+      </c>
       <c r="N10" s="9" t="n"/>
-      <c r="O10" s="9" t="n"/>
+      <c r="O10" s="30" t="inlineStr">
+        <is>
+          <t>support.easybill.de/hc/de/articles/13571616499228 und /14557057264412</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
@@ -1448,9 +1604,10 @@
       <c r="O26" s="13" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="A1:O1"/>
     <mergeCell ref="A4:O4"/>
+    <mergeCell ref="A3:O3"/>
     <mergeCell ref="A2:O2"/>
   </mergeCells>
   <dataValidations count="2">
@@ -1890,12 +2047,12 @@
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A29:E29"/>
-    <mergeCell ref="A18:E18"/>
     <mergeCell ref="A24:E24"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A5:E5"/>
     <mergeCell ref="A14:E14"/>
+    <mergeCell ref="A18:E18"/>
     <mergeCell ref="A9:E9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/erechnung/E-Rechnung_Arbeitsmappe.xlsx
+++ b/erechnung/E-Rechnung_Arbeitsmappe.xlsx
@@ -226,7 +226,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -302,6 +302,13 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1017,7 +1024,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="30" customHeight="1">
+    <row r="9" ht="74" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
         <is>
           <t>WISO Mein Buero</t>
@@ -1033,18 +1040,62 @@
           <t>Kern</t>
         </is>
       </c>
-      <c r="D9" s="9" t="n"/>
-      <c r="E9" s="9" t="n"/>
-      <c r="F9" s="9" t="n"/>
-      <c r="G9" s="9" t="n"/>
-      <c r="H9" s="9" t="n"/>
-      <c r="I9" s="9" t="n"/>
-      <c r="J9" s="9" t="n"/>
-      <c r="K9" s="9" t="n"/>
-      <c r="L9" s="9" t="n"/>
-      <c r="M9" s="9" t="n"/>
+      <c r="D9" s="30" t="inlineStr">
+        <is>
+          <t>04.09.2026</t>
+        </is>
+      </c>
+      <c r="E9" s="32" t="inlineStr">
+        <is>
+          <t>— noch offen —</t>
+        </is>
+      </c>
+      <c r="F9" s="30" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="G9" s="30" t="inlineStr">
+        <is>
+          <t>ZUGFeRD automatisch, XRechnung als XML-Download</t>
+        </is>
+      </c>
+      <c r="H9" s="30" t="inlineStr">
+        <is>
+          <t>Einstellungen &gt; Meine Firma &gt; E-Rechnungen</t>
+        </is>
+      </c>
+      <c r="I9" s="30" t="inlineStr">
+        <is>
+          <t>Bankverbindung und Kontaktdaten pflicht. Nur B2B — an Privatkunden keine E-Rechnung.</t>
+        </is>
+      </c>
+      <c r="J9" s="33" t="inlineStr">
+        <is>
+          <t>— noch offen — — WICHTIGSTE FRAGE, siehe Blatt 3</t>
+        </is>
+      </c>
+      <c r="K9" s="32" t="inlineStr">
+        <is>
+          <t>— noch offen —</t>
+        </is>
+      </c>
+      <c r="L9" s="32" t="inlineStr">
+        <is>
+          <t>— noch offen —</t>
+        </is>
+      </c>
+      <c r="M9" s="30" t="inlineStr">
+        <is>
+          <t>Jede Rechnung wird automatisch als ZUGFeRD erzeugt; die XRechnung-XML muss man nach dem Abschliessen separat herunterladen. Desktop- und Web-Version unterscheiden sich — vorher klaeren, welche der Kunde hat.</t>
+        </is>
+      </c>
       <c r="N9" s="9" t="n"/>
-      <c r="O9" s="9" t="n"/>
+      <c r="O9" s="30" t="inlineStr">
+        <is>
+          <t>handbuch.meinbuero.de/mbr-e-rechnung/e-rechnung-erstellen</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="86" customHeight="1">
       <c r="A10" s="6" t="inlineStr">
@@ -1119,7 +1170,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1">
+    <row r="11" ht="74" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
           <t>FastBill</t>
@@ -1135,20 +1186,64 @@
           <t>Kern</t>
         </is>
       </c>
-      <c r="D11" s="9" t="n"/>
-      <c r="E11" s="9" t="n"/>
-      <c r="F11" s="9" t="n"/>
-      <c r="G11" s="9" t="n"/>
-      <c r="H11" s="9" t="n"/>
-      <c r="I11" s="9" t="n"/>
-      <c r="J11" s="9" t="n"/>
-      <c r="K11" s="9" t="n"/>
-      <c r="L11" s="9" t="n"/>
-      <c r="M11" s="9" t="n"/>
+      <c r="D11" s="30" t="inlineStr">
+        <is>
+          <t>04.09.2026</t>
+        </is>
+      </c>
+      <c r="E11" s="32" t="inlineStr">
+        <is>
+          <t>— noch offen —</t>
+        </is>
+      </c>
+      <c r="F11" s="30" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="G11" s="30" t="inlineStr">
+        <is>
+          <t>XRechnung + ZUGFeRD</t>
+        </is>
+      </c>
+      <c r="H11" s="30" t="inlineStr">
+        <is>
+          <t>E-Rechnungs-Option aktivieren, dann wird bei „Rechnung erstellen“ automatisch beides erzeugt</t>
+        </is>
+      </c>
+      <c r="I11" s="30" t="inlineStr">
+        <is>
+          <t>Alle Pflichtangaben muessen gefuellt sein, sonst wird keine E-Rechnung erzeugt — welche genau: offen</t>
+        </is>
+      </c>
+      <c r="J11" s="33" t="inlineStr">
+        <is>
+          <t>— noch offen — — WICHTIGSTE FRAGE, siehe Blatt 3</t>
+        </is>
+      </c>
+      <c r="K11" s="32" t="inlineStr">
+        <is>
+          <t>— noch offen —</t>
+        </is>
+      </c>
+      <c r="L11" s="32" t="inlineStr">
+        <is>
+          <t>— noch offen —</t>
+        </is>
+      </c>
+      <c r="M11" s="30" t="inlineStr">
+        <is>
+          <t>Erzeugt ZUGFeRD und XRechnung gleichzeitig. Erzeugt sie nur, wenn alle Pflichtfelder gefuellt sind — sonst still kein E-Rechnungs-Ergebnis. Genau hinsehen.</t>
+        </is>
+      </c>
       <c r="N11" s="9" t="n"/>
-      <c r="O11" s="9" t="n"/>
-    </row>
-    <row r="12" ht="30" customHeight="1">
+      <c r="O11" s="30" t="inlineStr">
+        <is>
+          <t>support.fastbill.com/hc/de/articles/22209126147484</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="74" customHeight="1">
       <c r="A12" s="6" t="inlineStr">
         <is>
           <t>Billomat</t>
@@ -1164,20 +1259,64 @@
           <t>Kern</t>
         </is>
       </c>
-      <c r="D12" s="9" t="n"/>
-      <c r="E12" s="9" t="n"/>
-      <c r="F12" s="9" t="n"/>
-      <c r="G12" s="9" t="n"/>
-      <c r="H12" s="9" t="n"/>
-      <c r="I12" s="9" t="n"/>
-      <c r="J12" s="9" t="n"/>
-      <c r="K12" s="9" t="n"/>
-      <c r="L12" s="9" t="n"/>
-      <c r="M12" s="9" t="n"/>
+      <c r="D12" s="30" t="inlineStr">
+        <is>
+          <t>04.09.2026</t>
+        </is>
+      </c>
+      <c r="E12" s="32" t="inlineStr">
+        <is>
+          <t>— noch offen —</t>
+        </is>
+      </c>
+      <c r="F12" s="30" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="G12" s="30" t="inlineStr">
+        <is>
+          <t>XRechnung + ZUGFeRD</t>
+        </is>
+      </c>
+      <c r="H12" s="32" t="inlineStr">
+        <is>
+          <t>— noch offen —</t>
+        </is>
+      </c>
+      <c r="I12" s="32" t="inlineStr">
+        <is>
+          <t>— noch offen —</t>
+        </is>
+      </c>
+      <c r="J12" s="33" t="inlineStr">
+        <is>
+          <t>— noch offen — — WICHTIGSTE FRAGE, siehe Blatt 3</t>
+        </is>
+      </c>
+      <c r="K12" s="32" t="inlineStr">
+        <is>
+          <t>— noch offen —</t>
+        </is>
+      </c>
+      <c r="L12" s="32" t="inlineStr">
+        <is>
+          <t>— noch offen —</t>
+        </is>
+      </c>
+      <c r="M12" s="30" t="inlineStr">
+        <is>
+          <t>Unterstuetzung bestaetigt, Einrichtungsdetails noch nicht recherchiert.</t>
+        </is>
+      </c>
       <c r="N12" s="9" t="n"/>
-      <c r="O12" s="9" t="n"/>
-    </row>
-    <row r="13" ht="30" customHeight="1">
+      <c r="O12" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="74" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
         <is>
           <t>Papierkram</t>
@@ -1193,20 +1332,64 @@
           <t>Kern</t>
         </is>
       </c>
-      <c r="D13" s="9" t="n"/>
-      <c r="E13" s="9" t="n"/>
-      <c r="F13" s="9" t="n"/>
-      <c r="G13" s="9" t="n"/>
-      <c r="H13" s="9" t="n"/>
-      <c r="I13" s="9" t="n"/>
-      <c r="J13" s="9" t="n"/>
-      <c r="K13" s="9" t="n"/>
-      <c r="L13" s="9" t="n"/>
-      <c r="M13" s="9" t="n"/>
+      <c r="D13" s="30" t="inlineStr">
+        <is>
+          <t>04.09.2026</t>
+        </is>
+      </c>
+      <c r="E13" s="32" t="inlineStr">
+        <is>
+          <t>— noch offen —</t>
+        </is>
+      </c>
+      <c r="F13" s="32" t="inlineStr">
+        <is>
+          <t>— noch offen —</t>
+        </is>
+      </c>
+      <c r="G13" s="32" t="inlineStr">
+        <is>
+          <t>— noch offen —</t>
+        </is>
+      </c>
+      <c r="H13" s="32" t="inlineStr">
+        <is>
+          <t>— noch offen —</t>
+        </is>
+      </c>
+      <c r="I13" s="32" t="inlineStr">
+        <is>
+          <t>— noch offen —</t>
+        </is>
+      </c>
+      <c r="J13" s="33" t="inlineStr">
+        <is>
+          <t>— noch offen — — WICHTIGSTE FRAGE, siehe Blatt 3</t>
+        </is>
+      </c>
+      <c r="K13" s="32" t="inlineStr">
+        <is>
+          <t>— noch offen —</t>
+        </is>
+      </c>
+      <c r="L13" s="32" t="inlineStr">
+        <is>
+          <t>— noch offen —</t>
+        </is>
+      </c>
+      <c r="M13" s="30" t="inlineStr">
+        <is>
+          <t>Nichts Belastbares gefunden. Herstellerhilfe direkt aufrufen.</t>
+        </is>
+      </c>
       <c r="N13" s="9" t="n"/>
-      <c r="O13" s="9" t="n"/>
-    </row>
-    <row r="14" ht="30" customHeight="1">
+      <c r="O13" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="74" customHeight="1">
       <c r="A14" s="6" t="inlineStr">
         <is>
           <t>SumUp Rechnungen</t>
@@ -1222,20 +1405,64 @@
           <t>Kern</t>
         </is>
       </c>
-      <c r="D14" s="9" t="n"/>
-      <c r="E14" s="9" t="n"/>
-      <c r="F14" s="9" t="n"/>
-      <c r="G14" s="9" t="n"/>
-      <c r="H14" s="9" t="n"/>
-      <c r="I14" s="9" t="n"/>
-      <c r="J14" s="9" t="n"/>
-      <c r="K14" s="9" t="n"/>
-      <c r="L14" s="9" t="n"/>
-      <c r="M14" s="9" t="n"/>
+      <c r="D14" s="30" t="inlineStr">
+        <is>
+          <t>04.09.2026</t>
+        </is>
+      </c>
+      <c r="E14" s="32" t="inlineStr">
+        <is>
+          <t>— noch offen —</t>
+        </is>
+      </c>
+      <c r="F14" s="32" t="inlineStr">
+        <is>
+          <t>— noch offen —</t>
+        </is>
+      </c>
+      <c r="G14" s="32" t="inlineStr">
+        <is>
+          <t>— noch offen —</t>
+        </is>
+      </c>
+      <c r="H14" s="32" t="inlineStr">
+        <is>
+          <t>— noch offen —</t>
+        </is>
+      </c>
+      <c r="I14" s="32" t="inlineStr">
+        <is>
+          <t>— noch offen —</t>
+        </is>
+      </c>
+      <c r="J14" s="33" t="inlineStr">
+        <is>
+          <t>— noch offen — — WICHTIGSTE FRAGE, siehe Blatt 3</t>
+        </is>
+      </c>
+      <c r="K14" s="32" t="inlineStr">
+        <is>
+          <t>— noch offen —</t>
+        </is>
+      </c>
+      <c r="L14" s="32" t="inlineStr">
+        <is>
+          <t>— noch offen —</t>
+        </is>
+      </c>
+      <c r="M14" s="30" t="inlineStr">
+        <is>
+          <t>Nichts Belastbares gefunden. Eher Kleinstgewerbe — pruefen, ob die Zielgruppe ueberhaupt zahlt.</t>
+        </is>
+      </c>
       <c r="N14" s="9" t="n"/>
-      <c r="O14" s="9" t="n"/>
-    </row>
-    <row r="15" ht="30" customHeight="1">
+      <c r="O14" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="74" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
           <t>Collmex</t>
@@ -1251,18 +1478,62 @@
           <t>Kern</t>
         </is>
       </c>
-      <c r="D15" s="9" t="n"/>
-      <c r="E15" s="9" t="n"/>
-      <c r="F15" s="9" t="n"/>
-      <c r="G15" s="9" t="n"/>
-      <c r="H15" s="9" t="n"/>
-      <c r="I15" s="9" t="n"/>
-      <c r="J15" s="9" t="n"/>
-      <c r="K15" s="9" t="n"/>
-      <c r="L15" s="9" t="n"/>
-      <c r="M15" s="9" t="n"/>
+      <c r="D15" s="30" t="inlineStr">
+        <is>
+          <t>04.09.2026</t>
+        </is>
+      </c>
+      <c r="E15" s="32" t="inlineStr">
+        <is>
+          <t>— noch offen —</t>
+        </is>
+      </c>
+      <c r="F15" s="32" t="inlineStr">
+        <is>
+          <t>— noch offen —</t>
+        </is>
+      </c>
+      <c r="G15" s="32" t="inlineStr">
+        <is>
+          <t>— noch offen —</t>
+        </is>
+      </c>
+      <c r="H15" s="32" t="inlineStr">
+        <is>
+          <t>— noch offen —</t>
+        </is>
+      </c>
+      <c r="I15" s="32" t="inlineStr">
+        <is>
+          <t>— noch offen —</t>
+        </is>
+      </c>
+      <c r="J15" s="33" t="inlineStr">
+        <is>
+          <t>— noch offen — — WICHTIGSTE FRAGE, siehe Blatt 3</t>
+        </is>
+      </c>
+      <c r="K15" s="32" t="inlineStr">
+        <is>
+          <t>— noch offen —</t>
+        </is>
+      </c>
+      <c r="L15" s="32" t="inlineStr">
+        <is>
+          <t>— noch offen —</t>
+        </is>
+      </c>
+      <c r="M15" s="30" t="inlineStr">
+        <is>
+          <t>Nichts Belastbares gefunden. Collmex ist im Handwerk verbreitet — lohnt eigene Recherche.</t>
+        </is>
+      </c>
       <c r="N15" s="9" t="n"/>
-      <c r="O15" s="9" t="n"/>
+      <c r="O15" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="10" t="inlineStr">
@@ -2139,7 +2410,7 @@
       </c>
       <c r="E5" s="9" t="n"/>
     </row>
-    <row r="6" ht="52" customHeight="1">
+    <row r="6" ht="90" customHeight="1">
       <c r="A6" s="22" t="inlineStr">
         <is>
           <t>2</t>
@@ -2155,9 +2426,9 @@
           <t>Steuersatz 0 %, aber Steuerkategorie steht auf „S“, oder der Hinweistext auf die Steuerschuldnerschaft des Leistungsempfaengers fehlt.</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>Kategorie „AE“ setzen und Befreiungsgrund als Text hinterlegen. Bei Baubetrieben der mit Abstand haeufigste Fehler — hier zuerst hinsehen. Ob § 13b gilt, entscheidet der Steuerberater, nicht du.</t>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>Vier Angaben muessen zusammenpassen: Steuerkategorie „AE“, Steuersatz 0, Befreiungsgrund-Code „VATEX-EU-AE“ und der Befreiungstext „Steuerschuldnerschaft des Leistungsempfaengers“. Pruefen, ob die Software das automatisch setzt, sobald der Kunde als §13b-pflichtig markiert ist. ACHTUNG: Lexware Office kann §13b derzeit gar nicht als E-Rechnung ausgeben — siehe Blatt 1. Ob §13b gilt, entscheidet der Steuerberater, nicht du.</t>
         </is>
       </c>
       <c r="E6" s="9" t="n"/>
@@ -2361,7 +2632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2651,14 +2922,37 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="34" t="inlineStr">
+        <is>
+          <t>Zum Leser auf der Website — ehrlich eingeordnet</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="32" customHeight="1">
+      <c r="A27" s="35" t="inlineStr">
+        <is>
+          <t>•  Kostenlose E-Rechnungs-Betrachter gibt es bereits: Quba Viewer (vom Wirtschaftsministerium empfohlen), RIB Viewer, Mustang. Dein Leser ist technisch nichts Einzigartiges.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="32" customHeight="1">
+      <c r="A28" s="35" t="inlineStr">
+        <is>
+          <t>•  Sein Wert liegt nicht in der Funktion, sondern darin, dass er auf DEINER Seite steht und dort das Gespraech eroeffnet. Verkaufe nie den Betrachter — verkaufe die Einrichtung.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="8">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A23:D23"/>
+    <mergeCell ref="A27:D27"/>
     <mergeCell ref="A22:D22"/>
     <mergeCell ref="A21:D21"/>
     <mergeCell ref="A24:D24"/>
     <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A28:D28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/erechnung/E-Rechnung_Arbeitsmappe.xlsx
+++ b/erechnung/E-Rechnung_Arbeitsmappe.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="18">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -127,6 +127,17 @@
       <color rgb="00A93C1B"/>
       <sz val="12"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="0055605A"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00A93C1B"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -226,7 +237,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -310,6 +321,16 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1899,7 +1920,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2000,42 +2021,42 @@
       <c r="D8" s="21" t="n"/>
       <c r="E8" s="21" t="n"/>
     </row>
-    <row r="9">
-      <c r="A9" s="15" t="inlineStr">
-        <is>
-          <t>Bestandsaufnahme</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="n"/>
-      <c r="C9" s="16" t="n"/>
-      <c r="D9" s="16" t="n"/>
-      <c r="E9" s="17" t="n"/>
+    <row r="9" ht="26" customHeight="1">
+      <c r="A9" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" s="19" t="n"/>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>Rechnet der Betrieb ueberwiegend Kleinbetraege unter 250 € brutto ab? Dann ist er weitgehend gar nicht betroffen — vorher klaeren, nicht erst im Gespraech</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="n"/>
+      <c r="E9" s="21" t="n"/>
     </row>
     <row r="10" ht="26" customHeight="1">
       <c r="A10" s="18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B10" s="19" t="n"/>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>Rechnungsprogramm und Version am Bildschirm bestaetigen lassen</t>
+          <t>Nur Privatkunden? Dann besteht keine Ausstellungspflicht. Mischbetriebe nur fuer den gewerblichen Teil</t>
         </is>
       </c>
       <c r="D10" s="21" t="n"/>
       <c r="E10" s="21" t="n"/>
     </row>
-    <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="18" t="n">
-        <v>5</v>
-      </c>
-      <c r="B11" s="19" t="n"/>
-      <c r="C11" s="20" t="inlineStr">
-        <is>
-          <t>Rechnet der Betrieb nach § 13b ab (Bauleistungen)? Wenn ja: hoechste Fehlerquelle</t>
-        </is>
-      </c>
-      <c r="D11" s="21" t="n"/>
-      <c r="E11" s="21" t="n"/>
+    <row r="11">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>Bestandsaufnahme</t>
+        </is>
+      </c>
+      <c r="B11" s="16" t="n"/>
+      <c r="C11" s="16" t="n"/>
+      <c r="D11" s="16" t="n"/>
+      <c r="E11" s="17" t="n"/>
     </row>
     <row r="12" ht="26" customHeight="1">
       <c r="A12" s="18" t="n">
@@ -2044,7 +2065,7 @@
       <c r="B12" s="19" t="n"/>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>Behoerden oder oeffentliche Auftraggeber unter den Kunden? Dann Leitweg-ID noetig</t>
+          <t>Rechnungsprogramm und Version am Bildschirm bestaetigen lassen</t>
         </is>
       </c>
       <c r="D12" s="21" t="n"/>
@@ -2057,48 +2078,48 @@
       <c r="B13" s="19" t="n"/>
       <c r="C13" s="20" t="inlineStr">
         <is>
-          <t>Eingehende E-Rechnungen: wo landen die heute? (Empfangspflicht gilt seit 2025)</t>
+          <t>Rechnet der Betrieb nach § 13b ab (Bauleistungen)? Wenn ja: hoechste Fehlerquelle</t>
         </is>
       </c>
       <c r="D13" s="21" t="n"/>
       <c r="E13" s="21" t="n"/>
     </row>
-    <row r="14">
-      <c r="A14" s="15" t="inlineStr">
-        <is>
-          <t>Einrichtung Empfang</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="n"/>
-      <c r="C14" s="16" t="n"/>
-      <c r="D14" s="16" t="n"/>
-      <c r="E14" s="17" t="n"/>
+    <row r="14" ht="26" customHeight="1">
+      <c r="A14" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="B14" s="19" t="n"/>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>Behoerden oder oeffentliche Auftraggeber unter den Kunden? Dann Leitweg-ID noetig</t>
+        </is>
+      </c>
+      <c r="D14" s="21" t="n"/>
+      <c r="E14" s="21" t="n"/>
     </row>
     <row r="15" ht="26" customHeight="1">
       <c r="A15" s="18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B15" s="19" t="n"/>
       <c r="C15" s="20" t="inlineStr">
         <is>
-          <t>Eigene Adresse fuer eingehende E-Rechnungen einrichten</t>
+          <t>Eingehende E-Rechnungen: wo landen die heute? (Empfangspflicht gilt seit 2025)</t>
         </is>
       </c>
       <c r="D15" s="21" t="n"/>
       <c r="E15" s="21" t="n"/>
     </row>
-    <row r="16" ht="26" customHeight="1">
-      <c r="A16" s="18" t="n">
-        <v>9</v>
-      </c>
-      <c r="B16" s="19" t="n"/>
-      <c r="C16" s="20" t="inlineStr">
-        <is>
-          <t>Ablage festlegen — wohin gehoert die XML-Datei, wie lange aufbewahren</t>
-        </is>
-      </c>
-      <c r="D16" s="21" t="n"/>
-      <c r="E16" s="21" t="n"/>
+    <row r="16">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>Einrichtung Empfang</t>
+        </is>
+      </c>
+      <c r="B16" s="16" t="n"/>
+      <c r="C16" s="16" t="n"/>
+      <c r="D16" s="16" t="n"/>
+      <c r="E16" s="17" t="n"/>
     </row>
     <row r="17" ht="26" customHeight="1">
       <c r="A17" s="18" t="n">
@@ -2107,48 +2128,48 @@
       <c r="B17" s="19" t="n"/>
       <c r="C17" s="20" t="inlineStr">
         <is>
-          <t>Leseweg zeigen: wie macht das Buero eine XML-Datei lesbar</t>
+          <t>Eigene Adresse fuer eingehende E-Rechnungen einrichten</t>
         </is>
       </c>
       <c r="D17" s="21" t="n"/>
       <c r="E17" s="21" t="n"/>
     </row>
-    <row r="18">
-      <c r="A18" s="15" t="inlineStr">
-        <is>
-          <t>Einrichtung Versand</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="n"/>
-      <c r="C18" s="16" t="n"/>
-      <c r="D18" s="16" t="n"/>
-      <c r="E18" s="17" t="n"/>
+    <row r="18" ht="26" customHeight="1">
+      <c r="A18" s="18" t="n">
+        <v>11</v>
+      </c>
+      <c r="B18" s="19" t="n"/>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>Ablage festlegen — wohin gehoert die XML-Datei, wie lange aufbewahren</t>
+        </is>
+      </c>
+      <c r="D18" s="21" t="n"/>
+      <c r="E18" s="21" t="n"/>
     </row>
     <row r="19" ht="26" customHeight="1">
       <c r="A19" s="18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B19" s="19" t="n"/>
       <c r="C19" s="20" t="inlineStr">
         <is>
-          <t>E-Rechnung im Programm aktivieren (Menuepfad von Blatt 1)</t>
+          <t>Leseweg zeigen: wie macht das Buero eine XML-Datei lesbar</t>
         </is>
       </c>
       <c r="D19" s="21" t="n"/>
       <c r="E19" s="21" t="n"/>
     </row>
-    <row r="20" ht="26" customHeight="1">
-      <c r="A20" s="18" t="n">
-        <v>12</v>
-      </c>
-      <c r="B20" s="19" t="n"/>
-      <c r="C20" s="20" t="inlineStr">
-        <is>
-          <t>Stammdaten pruefen: USt-IdNr., vollstaendige Anschrift, IBAN, Steuernummer</t>
-        </is>
-      </c>
-      <c r="D20" s="21" t="n"/>
-      <c r="E20" s="21" t="n"/>
+    <row r="20">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>Einrichtung Versand</t>
+        </is>
+      </c>
+      <c r="B20" s="16" t="n"/>
+      <c r="C20" s="16" t="n"/>
+      <c r="D20" s="16" t="n"/>
+      <c r="E20" s="17" t="n"/>
     </row>
     <row r="21" ht="26" customHeight="1">
       <c r="A21" s="18" t="n">
@@ -2157,7 +2178,7 @@
       <c r="B21" s="19" t="n"/>
       <c r="C21" s="20" t="inlineStr">
         <is>
-          <t>Steuerschluessel pruefen — besonders § 13b und § 19 (Blatt 3)</t>
+          <t>E-Rechnung im Programm aktivieren (Menuepfad von Blatt 1)</t>
         </is>
       </c>
       <c r="D21" s="21" t="n"/>
@@ -2170,7 +2191,7 @@
       <c r="B22" s="19" t="n"/>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>Leitweg-ID im Kundenstamm hinterlegen, wo noetig</t>
+          <t>Stammdaten pruefen: USt-IdNr., vollstaendige Anschrift, IBAN, Steuernummer</t>
         </is>
       </c>
       <c r="D22" s="21" t="n"/>
@@ -2183,48 +2204,48 @@
       <c r="B23" s="19" t="n"/>
       <c r="C23" s="20" t="inlineStr">
         <is>
-          <t>Einheiten pruefen: Codes statt Freitext</t>
+          <t>Steuerschluessel pruefen — besonders § 13b und § 19 (Blatt 3)</t>
         </is>
       </c>
       <c r="D23" s="21" t="n"/>
       <c r="E23" s="21" t="n"/>
     </row>
-    <row r="24">
-      <c r="A24" s="15" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="n"/>
-      <c r="C24" s="16" t="n"/>
-      <c r="D24" s="16" t="n"/>
-      <c r="E24" s="17" t="n"/>
+    <row r="24" ht="26" customHeight="1">
+      <c r="A24" s="18" t="n">
+        <v>16</v>
+      </c>
+      <c r="B24" s="19" t="n"/>
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>Leitweg-ID im Kundenstamm hinterlegen, wo noetig</t>
+        </is>
+      </c>
+      <c r="D24" s="21" t="n"/>
+      <c r="E24" s="21" t="n"/>
     </row>
     <row r="25" ht="26" customHeight="1">
       <c r="A25" s="18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B25" s="19" t="n"/>
       <c r="C25" s="20" t="inlineStr">
         <is>
-          <t>Testrechnung erzeugen — mit einer Position § 13b, wenn zutreffend</t>
+          <t>Einheiten pruefen: Codes statt Freitext</t>
         </is>
       </c>
       <c r="D25" s="21" t="n"/>
       <c r="E25" s="21" t="n"/>
     </row>
-    <row r="26" ht="26" customHeight="1">
-      <c r="A26" s="18" t="n">
-        <v>17</v>
-      </c>
-      <c r="B26" s="19" t="n"/>
-      <c r="C26" s="20" t="inlineStr">
-        <is>
-          <t>Gegen den Validator pruefen (KoSIT / Validierungsdienst)</t>
-        </is>
-      </c>
-      <c r="D26" s="21" t="n"/>
-      <c r="E26" s="21" t="n"/>
+    <row r="26">
+      <c r="A26" s="15" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="B26" s="16" t="n"/>
+      <c r="C26" s="16" t="n"/>
+      <c r="D26" s="16" t="n"/>
+      <c r="E26" s="17" t="n"/>
     </row>
     <row r="27" ht="26" customHeight="1">
       <c r="A27" s="18" t="n">
@@ -2233,7 +2254,7 @@
       <c r="B27" s="19" t="n"/>
       <c r="C27" s="20" t="inlineStr">
         <is>
-          <t>Fehler beheben, bis sie sauber durchlaeuft — alle Befunde in Blatt 3 nachtragen</t>
+          <t>Testrechnung erzeugen — mit einer Position § 13b, wenn zutreffend</t>
         </is>
       </c>
       <c r="D27" s="21" t="n"/>
@@ -2246,48 +2267,48 @@
       <c r="B28" s="19" t="n"/>
       <c r="C28" s="20" t="inlineStr">
         <is>
-          <t>Testrechnung an eine echte Kundenadresse senden und Empfang bestaetigen lassen</t>
+          <t>Gegen den Validator pruefen (KoSIT / Validierungsdienst)</t>
         </is>
       </c>
       <c r="D28" s="21" t="n"/>
       <c r="E28" s="21" t="n"/>
     </row>
-    <row r="29">
-      <c r="A29" s="15" t="inlineStr">
-        <is>
-          <t>Abschluss</t>
-        </is>
-      </c>
-      <c r="B29" s="16" t="n"/>
-      <c r="C29" s="16" t="n"/>
-      <c r="D29" s="16" t="n"/>
-      <c r="E29" s="17" t="n"/>
+    <row r="29" ht="26" customHeight="1">
+      <c r="A29" s="18" t="n">
+        <v>20</v>
+      </c>
+      <c r="B29" s="19" t="n"/>
+      <c r="C29" s="20" t="inlineStr">
+        <is>
+          <t>Fehler beheben, bis sie sauber durchlaeuft — alle Befunde in Blatt 3 nachtragen</t>
+        </is>
+      </c>
+      <c r="D29" s="21" t="n"/>
+      <c r="E29" s="21" t="n"/>
     </row>
     <row r="30" ht="26" customHeight="1">
       <c r="A30" s="18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B30" s="19" t="n"/>
       <c r="C30" s="20" t="inlineStr">
         <is>
-          <t>Eine Seite Anleitung fuer das Buero uebergeben</t>
+          <t>Testrechnung an eine echte Kundenadresse senden und Empfang bestaetigen lassen</t>
         </is>
       </c>
       <c r="D30" s="21" t="n"/>
       <c r="E30" s="21" t="n"/>
     </row>
-    <row r="31" ht="26" customHeight="1">
-      <c r="A31" s="18" t="n">
-        <v>21</v>
-      </c>
-      <c r="B31" s="19" t="n"/>
-      <c r="C31" s="20" t="inlineStr">
-        <is>
-          <t>Abnahme durch den Kunden bestaetigen lassen (schriftlich, kurz)</t>
-        </is>
-      </c>
-      <c r="D31" s="21" t="n"/>
-      <c r="E31" s="21" t="n"/>
+    <row r="31">
+      <c r="A31" s="15" t="inlineStr">
+        <is>
+          <t>Abschluss</t>
+        </is>
+      </c>
+      <c r="B31" s="16" t="n"/>
+      <c r="C31" s="16" t="n"/>
+      <c r="D31" s="16" t="n"/>
+      <c r="E31" s="17" t="n"/>
     </row>
     <row r="32" ht="26" customHeight="1">
       <c r="A32" s="18" t="n">
@@ -2296,7 +2317,7 @@
       <c r="B32" s="19" t="n"/>
       <c r="C32" s="20" t="inlineStr">
         <is>
-          <t>Rechnung stellen</t>
+          <t>Eine Seite Anleitung fuer das Buero uebergeben</t>
         </is>
       </c>
       <c r="D32" s="21" t="n"/>
@@ -2309,22 +2330,48 @@
       <c r="B33" s="19" t="n"/>
       <c r="C33" s="20" t="inlineStr">
         <is>
-          <t>Blatt 1 ergaenzen: was war neu an diesem System?</t>
+          <t>Abnahme durch den Kunden bestaetigen lassen (schriftlich, kurz)</t>
         </is>
       </c>
       <c r="D33" s="21" t="n"/>
       <c r="E33" s="21" t="n"/>
     </row>
+    <row r="34" ht="26" customHeight="1">
+      <c r="A34" s="18" t="n">
+        <v>24</v>
+      </c>
+      <c r="B34" s="19" t="n"/>
+      <c r="C34" s="20" t="inlineStr">
+        <is>
+          <t>Rechnung stellen</t>
+        </is>
+      </c>
+      <c r="D34" s="21" t="n"/>
+      <c r="E34" s="21" t="n"/>
+    </row>
+    <row r="35" ht="26" customHeight="1">
+      <c r="A35" s="18" t="n">
+        <v>25</v>
+      </c>
+      <c r="B35" s="19" t="n"/>
+      <c r="C35" s="20" t="inlineStr">
+        <is>
+          <t>Blatt 1 ergaenzen: was war neu an diesem System?</t>
+        </is>
+      </c>
+      <c r="D35" s="21" t="n"/>
+      <c r="E35" s="21" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A29:E29"/>
-    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="A26:E26"/>
     <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A11:E11"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A14:E14"/>
-    <mergeCell ref="A18:E18"/>
-    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A31:E31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2632,7 +2679,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2943,13 +2990,126 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>Ausnahmen — wer die Rechnung NICHT elektronisch stellen muss</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="26" customHeight="1">
+      <c r="A31" s="36" t="inlineStr">
+        <is>
+          <t>Vor jedem Angebot pruefen. Wer hier hineinfaellt, hat ein kleineres Problem als geschildert — das offen zu sagen kostet einen Auftrag und bringt Glaubwuerdigkeit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Ausnahme</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>Was das bedeutet</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>Folge fuers Angebot</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr"/>
+    </row>
+    <row r="34" ht="44" customHeight="1">
+      <c r="A34" s="37" t="inlineStr">
+        <is>
+          <t>Kleinbetragsrechnungen bis 250 € brutto</t>
+        </is>
+      </c>
+      <c r="B34" s="38" t="inlineStr">
+        <is>
+          <t>Rechnungen bis 250 € brutto sind von der Ausstellungspflicht ausgenommen. Der Betrieb darf sie weiterhin als Papier oder PDF stellen.</t>
+        </is>
+      </c>
+      <c r="C34" s="38" t="inlineStr">
+        <is>
+          <t>Wer fast nur Kleinbetraege abrechnet, braucht kaum etwas. Ehrlich sagen. Wer beides hat, braucht die Umstellung trotzdem — dann fuer den Rest.</t>
+        </is>
+      </c>
+      <c r="D34" s="19" t="n"/>
+    </row>
+    <row r="35" ht="44" customHeight="1">
+      <c r="A35" s="37" t="inlineStr">
+        <is>
+          <t>Rechnungen an Privatpersonen (B2C)</t>
+        </is>
+      </c>
+      <c r="B35" s="38" t="inlineStr">
+        <is>
+          <t>Die Pflicht gilt nur zwischen inlaendischen Unternehmen. An Privatkunden gibt es keine E-Rechnungspflicht.</t>
+        </is>
+      </c>
+      <c r="C35" s="38" t="inlineStr">
+        <is>
+          <t>Ein reiner Privatkundenbetrieb ist nicht betroffen. Mischbetriebe schon — aber nur fuer den gewerblichen Teil.</t>
+        </is>
+      </c>
+      <c r="D35" s="19" t="n"/>
+    </row>
+    <row r="36" ht="44" customHeight="1">
+      <c r="A36" s="37" t="inlineStr">
+        <is>
+          <t>Bestimmte steuerfreie Umsaetze nach § 4 UStG</t>
+        </is>
+      </c>
+      <c r="B36" s="38" t="inlineStr">
+        <is>
+          <t>Einzelne nach § 4 UStG steuerfreie Leistungen sind ausgenommen. Welche genau, entscheidet der Steuerberater.</t>
+        </is>
+      </c>
+      <c r="C36" s="38" t="inlineStr">
+        <is>
+          <t>Nicht selbst beurteilen. An den Steuerberater verweisen — das ist Steuerrecht, nicht Technik.</t>
+        </is>
+      </c>
+      <c r="D36" s="19" t="n"/>
+    </row>
+    <row r="37" ht="44" customHeight="1">
+      <c r="A37" s="37" t="inlineStr">
+        <is>
+          <t>Kleinunternehmer nach § 19 UStG</t>
+        </is>
+      </c>
+      <c r="B37" s="38" t="inlineStr">
+        <is>
+          <t>Dauerhaft von der Ausstellungspflicht befreit. Empfangen muessen sie trotzdem, und zwar schon seit 2025.</t>
+        </is>
+      </c>
+      <c r="C37" s="38" t="inlineStr">
+        <is>
+          <t>Kein Versandpaket anbieten. Stattdessen das kleine Empfangspaket — die Pflicht laeuft bereits.</t>
+        </is>
+      </c>
+      <c r="D37" s="19" t="n"/>
+    </row>
+    <row r="39" ht="32" customHeight="1">
+      <c r="A39" s="39" t="inlineStr">
+        <is>
+          <t>Die Frage am Telefon dafuer: „Wie hoch ist bei Ihnen eine durchschnittliche Rechnung, und geht die an Betriebe oder an Privatleute?“ — beantwortet beide Ausnahmen auf einmal.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="10">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A23:D23"/>
     <mergeCell ref="A27:D27"/>
+    <mergeCell ref="A31:D31"/>
     <mergeCell ref="A22:D22"/>
     <mergeCell ref="A21:D21"/>
+    <mergeCell ref="A39:D39"/>
     <mergeCell ref="A24:D24"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A28:D28"/>

--- a/erechnung/E-Rechnung_Arbeitsmappe.xlsx
+++ b/erechnung/E-Rechnung_Arbeitsmappe.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="1 Systeme" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="2 Kundencheckliste" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="3 Fehlerkatalog" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="4 Angebot &amp; Regeln" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1 Systeme" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2 Kundencheckliste" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3 Fehlerkatalog" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4 Angebot &amp; Regeln" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -915,7 +915,7 @@
       </c>
       <c r="D7" s="30" t="inlineStr">
         <is>
-          <t>04.09.2026</t>
+          <t>04.09.2026 + eigener Test 11.09.2026</t>
         </is>
       </c>
       <c r="E7" s="30" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="M7" s="31" t="inlineStr">
         <is>
-          <t>GROESSTER PUNKT: Baubetriebe mit §13b koennen mit Lexware Office ab 2028 keine gueltige E-Rechnung stellen. Bis 2027/2028 ist PDF noch zulaessig, danach nicht mehr. Das ist kein Einrichtungsauftrag, sondern ein Gespraech ueber einen Systemwechsel.</t>
+          <t>GROESSTER PUNKT: Baubetriebe mit §13b koennen mit Lexware Office ab 2028 keine gueltige E-Rechnung stellen. Bis 2027/2028 ist PDF noch zulaessig, danach nicht mehr. Das ist kein Einrichtungsauftrag, sondern ein Gespraech ueber einen Systemwechsel. EIGENER TEST am 11.09.2026 bestaetigt: Testkonto, Kunde mit Haken 'Steuerfreie Rechnungen erlauben', Rechnung wird korrekt als 'Bauleistungen §13b' erkannt und zeigt den richtigen Reverse-Charge-Text. Aber im Mailversand haengt trotzdem nur eine PDF, keine XRechnung/ZUGFeRD-Datei. Befund von Lexware selbst damit durch eigenen Test bestaetigt, nicht nur zitiert.</t>
         </is>
       </c>
       <c r="N7" s="30" t="n">

--- a/erechnung/E-Rechnung_Arbeitsmappe.xlsx
+++ b/erechnung/E-Rechnung_Arbeitsmappe.xlsx
@@ -960,7 +960,7 @@
       </c>
       <c r="M7" s="31" t="inlineStr">
         <is>
-          <t>GROESSTER PUNKT: Baubetriebe mit §13b koennen mit Lexware Office ab 2028 keine gueltige E-Rechnung stellen. Bis 2027/2028 ist PDF noch zulaessig, danach nicht mehr. Das ist kein Einrichtungsauftrag, sondern ein Gespraech ueber einen Systemwechsel. EIGENER TEST am 11.09.2026 bestaetigt: Testkonto, Kunde mit Haken 'Steuerfreie Rechnungen erlauben', Rechnung wird korrekt als 'Bauleistungen §13b' erkannt und zeigt den richtigen Reverse-Charge-Text. Aber im Mailversand haengt trotzdem nur eine PDF, keine XRechnung/ZUGFeRD-Datei. Befund von Lexware selbst damit durch eigenen Test bestaetigt, nicht nur zitiert.</t>
+          <t>GROESSTER PUNKT: Baubetriebe mit §13b koennen mit Lexware Office ab 2028 keine gueltige E-Rechnung stellen. Bis 2027/2028 ist PDF noch zulaessig, danach nicht mehr. Das ist kein Einrichtungsauftrag, sondern ein Gespraech ueber einen Systemwechsel. EIGENER TEST am 11.09.2026 bestaetigt: Testkonto, Kunde mit Haken 'Steuerfreie Rechnungen erlauben', Rechnung wird korrekt als 'Bauleistungen §13b' erkannt und zeigt den richtigen Reverse-Charge-Text. Aber im Mailversand haengt trotzdem nur eine PDF, keine XRechnung/ZUGFeRD-Datei. Befund von Lexware selbst damit durch eigenen Test bestaetigt, nicht nur zitiert. ERWEITERTER TEST 11.09.2026: Auch bei einer GANZ NORMALEN Rechnung (19%, kein §13b) haengt sowohl beim direkten Download als auch beim ECHTEN Versand ueber lexoffice an die eigene Mailadresse nur eine reine PDF ohne eingebettete XML. Mit dem eigenen Leser geprueft (erkennt ZUGFeRD normalerweise zuverlaessig, siehe Beispieldatei). Auch das Kundencenter bietet keinen separaten E-Rechnung-Download, nur PDF oder Anruf. Offen bleibt, ob das ein Limit der kostenlosen Testphase (Lexware Office XL Trial) ist oder auch im bezahlten Konto so laeuft — fuer die Kundenansprache ist das nicht entscheidend, siehe Verkaufsblatt.</t>
         </is>
       </c>
       <c r="N7" s="30" t="n">
